--- a/AAII_Financials/Quarterly/AII_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AII_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="92">
   <si>
     <t>AII</t>
   </si>
@@ -656,63 +656,64 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -731,38 +732,41 @@
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>115200</v>
+      </c>
+      <c r="E8" s="3">
         <v>90900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>68100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>62000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>74500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>71900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>67100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>46500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>46400</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -781,38 +785,41 @@
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>50600</v>
+      </c>
+      <c r="E9" s="3">
         <v>47700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>32100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>35900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>27500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>24000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>44600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>32800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>19200</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -831,38 +838,41 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>64600</v>
+      </c>
+      <c r="E10" s="3">
         <v>43200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>35900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>26100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>47000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>47900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>22500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>13700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>27200</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -881,8 +891,11 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -901,8 +914,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -951,8 +965,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1001,8 +1018,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1018,8 +1038,8 @@
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+      <c r="H14" s="3">
+        <v>1700</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -1051,28 +1071,31 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>300</v>
+      </c>
+      <c r="E15" s="3">
         <v>800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>500</v>
-      </c>
-      <c r="I15" s="3">
-        <v>700</v>
       </c>
       <c r="J15" s="3">
         <v>700</v>
@@ -1081,13 +1104,13 @@
         <v>700</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
+      <c r="N15" s="3">
+        <v>0</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>3</v>
@@ -1101,8 +1124,11 @@
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1118,38 +1144,39 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>68700</v>
+      </c>
+      <c r="E17" s="3">
         <v>63700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>38800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>43300</v>
       </c>
-      <c r="G17" s="3">
-        <v>50400</v>
-      </c>
       <c r="H17" s="3">
+        <v>48700</v>
+      </c>
+      <c r="I17" s="3">
         <v>29000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>56400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>40000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>26000</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1168,38 +1195,41 @@
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>46400</v>
+      </c>
+      <c r="E18" s="3">
         <v>27300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>29300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>18800</v>
       </c>
-      <c r="G18" s="3">
-        <v>24100</v>
-      </c>
       <c r="H18" s="3">
+        <v>25800</v>
+      </c>
+      <c r="I18" s="3">
         <v>42900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>10700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>20400</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1218,8 +1248,11 @@
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1238,8 +1271,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1288,43 +1322,46 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>46700</v>
+      </c>
+      <c r="E21" s="3">
         <v>28100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>30000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>19200</v>
       </c>
-      <c r="G21" s="3">
-        <v>24700</v>
-      </c>
       <c r="H21" s="3">
+        <v>26400</v>
+      </c>
+      <c r="I21" s="3">
         <v>43400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>11500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>7300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>21100</v>
       </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
       <c r="M21" s="3">
         <v>0</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
+      <c r="N21" s="3">
+        <v>0</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
@@ -1338,8 +1375,11 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1388,38 +1428,41 @@
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>46400</v>
+      </c>
+      <c r="E23" s="3">
         <v>27300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>29300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>18800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>24100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>42900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>10700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>20400</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1438,38 +1481,41 @@
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E24" s="3">
         <v>7300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-3400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5700</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1488,8 +1534,11 @@
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1538,38 +1587,41 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>34100</v>
+      </c>
+      <c r="E26" s="3">
         <v>19900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>20900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>13200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>27500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>38100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>8400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>14700</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1588,38 +1640,41 @@
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>34100</v>
+      </c>
+      <c r="E27" s="3">
         <v>19900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>20900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>13200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>27500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>35900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>14100</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1638,8 +1693,11 @@
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1688,8 +1746,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1723,8 +1784,8 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>3</v>
+      <c r="N29" s="3">
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>3</v>
@@ -1738,8 +1799,11 @@
       <c r="R29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1788,8 +1852,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1838,8 +1905,11 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1888,38 +1958,41 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>34100</v>
+      </c>
+      <c r="E33" s="3">
         <v>19900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>20900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>13200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>27500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>38100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>8400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>14700</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1938,8 +2011,11 @@
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1988,38 +2064,41 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>34100</v>
+      </c>
+      <c r="E35" s="3">
         <v>19900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>20900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>13200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>27500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>38100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>8400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>14700</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2038,43 +2117,46 @@
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2093,8 +2175,11 @@
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2113,8 +2198,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2133,32 +2219,33 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>288500</v>
+      </c>
+      <c r="E41" s="3">
         <v>171200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>203900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>144800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>259600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>236400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>173200</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2183,23 +2270,26 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E42" s="3">
         <v>2500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>18100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>27100</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -2218,8 +2308,8 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
+      <c r="N42" s="3">
+        <v>0</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
@@ -2233,32 +2323,35 @@
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>60600</v>
+      </c>
+      <c r="E43" s="3">
         <v>44400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>45000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>54200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>58600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>56500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>51600</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2283,8 +2376,11 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2333,32 +2429,35 @@
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>251100</v>
+      </c>
+      <c r="E45" s="3">
         <v>337200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>272500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>375100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>395500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>441600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>464300</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2383,32 +2482,35 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1179900</v>
+      </c>
+      <c r="E46" s="3">
         <v>768400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>854900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1084700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1296800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>917300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>963400</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2433,32 +2535,35 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>346400</v>
+      </c>
+      <c r="E47" s="3">
         <v>347300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>330500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>329900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>275400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>206200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>214000</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2483,32 +2588,35 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>47400</v>
+      </c>
+      <c r="E48" s="3">
         <v>42100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4300</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2533,13 +2641,16 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>22400</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
@@ -2562,8 +2673,8 @@
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
@@ -2583,8 +2694,11 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2633,8 +2747,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2683,32 +2800,35 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E52" s="3">
         <v>8400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>24900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>16400</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2733,8 +2853,11 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2783,32 +2906,35 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1612300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1175100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1225100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1433700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1591500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1134700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1198100</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2833,8 +2959,11 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2853,8 +2982,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2873,32 +3003,33 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>341600</v>
+      </c>
+      <c r="E57" s="3">
         <v>5400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>78500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>177600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>344800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>56300</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2923,37 +3054,40 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>300</v>
+      </c>
+      <c r="E58" s="3">
         <v>400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>400</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
@@ -2973,32 +3107,35 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>580100</v>
+      </c>
+      <c r="E59" s="3">
         <v>503500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>497700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>528700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>515100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>464500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>441500</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3023,32 +3160,35 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>922000</v>
+      </c>
+      <c r="E60" s="3">
         <v>509200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>577100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>706800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>861000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>467500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>498300</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3073,32 +3213,35 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>33200</v>
+      </c>
+      <c r="E61" s="3">
         <v>32800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>200</v>
-      </c>
-      <c r="F61" s="3">
-        <v>1200</v>
       </c>
       <c r="G61" s="3">
         <v>1200</v>
       </c>
       <c r="H61" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I61" s="3">
         <v>1300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3200</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -3108,8 +3251,8 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-      <c r="N61" s="3" t="s">
-        <v>3</v>
+      <c r="N61" s="3">
+        <v>0</v>
       </c>
       <c r="O61" s="3" t="s">
         <v>3</v>
@@ -3123,32 +3266,35 @@
       <c r="R61" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>287600</v>
+      </c>
+      <c r="E62" s="3">
         <v>297600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>310800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>409800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>427300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>479900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>533100</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3173,8 +3319,11 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3223,8 +3372,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3273,8 +3425,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3323,32 +3478,35 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1242800</v>
+      </c>
+      <c r="E66" s="3">
         <v>839600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>888100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1117800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1289600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>948700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1035800</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3373,8 +3531,11 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3393,8 +3554,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3443,8 +3605,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3493,8 +3658,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3528,8 +3696,8 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3" t="s">
-        <v>3</v>
+      <c r="N70" s="3">
+        <v>0</v>
       </c>
       <c r="O70" s="3" t="s">
         <v>3</v>
@@ -3543,8 +3711,11 @@
       <c r="R70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3593,32 +3764,35 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>263300</v>
+      </c>
+      <c r="E72" s="3">
         <v>229100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>229200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>208300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>195100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>175700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>152400</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3643,8 +3817,11 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3693,8 +3870,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3743,8 +3923,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3793,32 +3976,35 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>369500</v>
+      </c>
+      <c r="E76" s="3">
         <v>335500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>337000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>315900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>301900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>186100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>162400</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3843,8 +4029,11 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3893,43 +4082,46 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3948,38 +4140,41 @@
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>34100</v>
+      </c>
+      <c r="E81" s="3">
         <v>19900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>20900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>13200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>27500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>38100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>8400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>14700</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3998,8 +4193,11 @@
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4018,16 +4216,17 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>700</v>
+      </c>
+      <c r="E83" s="3">
         <v>500</v>
-      </c>
-      <c r="E83" s="3">
-        <v>700</v>
       </c>
       <c r="F83" s="3">
         <v>700</v>
@@ -4038,8 +4237,8 @@
       <c r="H83" s="3">
         <v>700</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
+      <c r="I83" s="3">
+        <v>700</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
@@ -4068,8 +4267,11 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4118,8 +4320,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4168,8 +4373,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4218,8 +4426,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4268,8 +4479,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4318,38 +4532,41 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>123100</v>
+      </c>
+      <c r="E89" s="3">
         <v>6800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>50200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-7500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>27400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>68100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>152700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-31000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>47400</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4368,8 +4585,11 @@
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4388,37 +4608,38 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1300</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-4500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-500</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-100</v>
       </c>
       <c r="I91" s="3">
         <v>-100</v>
       </c>
       <c r="J91" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
+      <c r="L91" s="3">
+        <v>-300</v>
       </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
@@ -4438,8 +4659,11 @@
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4488,8 +4712,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4538,38 +4765,41 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>9700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-84900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-68200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>8300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-42900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-18500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>46500</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4588,8 +4818,11 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4608,38 +4841,39 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>20000</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>8000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>14900</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>8000</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M96" s="3" t="s">
         <v>3</v>
       </c>
@@ -4658,8 +4892,11 @@
       <c r="R96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4708,8 +4945,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4758,8 +4998,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4808,38 +5051,41 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-20100</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-100</v>
       </c>
       <c r="F100" s="3">
         <v>-100</v>
       </c>
       <c r="G100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H100" s="3">
         <v>76900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-15000</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-100</v>
       </c>
       <c r="J100" s="3">
         <v>-100</v>
       </c>
       <c r="K100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L100" s="3">
         <v>-8100</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4858,8 +5104,11 @@
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4908,43 +5157,46 @@
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>117500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-17800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>59800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-92500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>36100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>61500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>109700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-49600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>85800</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
         <v>0</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
+      <c r="N102" s="3">
+        <v>0</v>
       </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
@@ -4956,6 +5208,9 @@
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
